--- a/exports/trend_1d/SHREECEM_full_report.xlsx
+++ b/exports/trend_1d/SHREECEM_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q76"/>
+  <dimension ref="A1:U76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>9.77</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42110</v>
+        <v>42111</v>
       </c>
       <c r="H2" t="n">
-        <v>10451.5</v>
+        <v>10039.1</v>
       </c>
       <c r="I2" t="n">
         <v>10111.26843376784</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K2" t="n">
-        <v>4.79</v>
+        <v>0.65</v>
       </c>
       <c r="L2" t="n">
         <v>7.56</v>
@@ -555,7 +578,7 @@
         <v>3.22</v>
       </c>
       <c r="N2" t="n">
-        <v>3.38</v>
+        <v>3.95</v>
       </c>
       <c r="O2" t="n">
         <v>7.68</v>
@@ -564,7 +587,19 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>15.3</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42137</v>
+        <v>42138</v>
       </c>
       <c r="H3" t="n">
-        <v>11088.15</v>
+        <v>11327.7</v>
       </c>
       <c r="I3" t="n">
         <v>11096.04373449667</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K3" t="n">
-        <v>-10.45</v>
+        <v>-12.84</v>
       </c>
       <c r="L3" t="n">
-        <v>14.8</v>
+        <v>15.05</v>
       </c>
       <c r="M3" t="n">
         <v>5.2</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>15.09</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42167</v>
+        <v>42170</v>
       </c>
       <c r="H4" t="n">
-        <v>10601.05</v>
+        <v>10489.15</v>
       </c>
       <c r="I4" t="n">
         <v>10510.32904380812</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K4" t="n">
-        <v>-6.41</v>
+        <v>-7.4</v>
       </c>
       <c r="L4" t="n">
-        <v>7.75</v>
+        <v>9.92</v>
       </c>
       <c r="M4" t="n">
         <v>3.79</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>12.06</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42201</v>
+        <v>42202</v>
       </c>
       <c r="H5" t="n">
-        <v>11575.65</v>
+        <v>11687.25</v>
       </c>
       <c r="I5" t="n">
         <v>11636.43746761889</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K5" t="n">
-        <v>-10.36</v>
+        <v>-11.42</v>
       </c>
       <c r="L5" t="n">
-        <v>11.45</v>
+        <v>12.46</v>
       </c>
       <c r="M5" t="n">
         <v>1.53</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>9.109999999999999</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42240</v>
+        <v>42241</v>
       </c>
       <c r="H6" t="n">
-        <v>10806.95</v>
+        <v>10540.85</v>
       </c>
       <c r="I6" t="n">
         <v>10622.84406970707</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K6" t="n">
-        <v>-7.53</v>
+        <v>-9.81</v>
       </c>
       <c r="L6" t="n">
-        <v>9.289999999999999</v>
+        <v>10.93</v>
       </c>
       <c r="M6" t="n">
         <v>3.89</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>14.14</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42263</v>
+        <v>42265</v>
       </c>
       <c r="H7" t="n">
-        <v>11497.9</v>
+        <v>12046.45</v>
       </c>
       <c r="I7" t="n">
         <v>11835.39740358588</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K7" t="n">
-        <v>-9.08</v>
+        <v>-14.28</v>
       </c>
       <c r="L7" t="n">
-        <v>10.71</v>
+        <v>18.59</v>
       </c>
       <c r="M7" t="n">
         <v>2.41</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>12.89</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42319</v>
+        <v>42321</v>
       </c>
       <c r="H8" t="n">
-        <v>11740</v>
+        <v>11282.3</v>
       </c>
       <c r="I8" t="n">
         <v>11375.76998233905</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.54</v>
+        <v>-6.34</v>
       </c>
       <c r="L8" t="n">
         <v>10.35</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42271</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>15.69</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42417</v>
+        <v>42418</v>
       </c>
       <c r="H9" t="n">
-        <v>10074.35</v>
+        <v>10894</v>
       </c>
       <c r="I9" t="n">
         <v>10866.46002178068</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K9" t="n">
-        <v>10.71</v>
+        <v>3.44</v>
       </c>
       <c r="L9" t="n">
         <v>5.62</v>
@@ -954,7 +1061,7 @@
         <v>3.76</v>
       </c>
       <c r="N9" t="n">
-        <v>4.28</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="O9" t="n">
         <v>-3.9</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>16.31</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42676</v>
+        <v>42677</v>
       </c>
       <c r="H10" t="n">
-        <v>16465.8</v>
+        <v>16122.15</v>
       </c>
       <c r="I10" t="n">
         <v>16416.70890869732</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K10" t="n">
-        <v>51.15</v>
+        <v>47.99</v>
       </c>
       <c r="L10" t="n">
         <v>9.119999999999999</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>172</v>
+        <v>173</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42425</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>10</v>
+      </c>
+      <c r="U10" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>10.33</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42752</v>
+        <v>42753</v>
       </c>
       <c r="H11" t="n">
-        <v>14966.6</v>
+        <v>15435.9</v>
       </c>
       <c r="I11" t="n">
         <v>15054.31481373943</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K11" t="n">
-        <v>7.17</v>
+        <v>4.26</v>
       </c>
       <c r="L11" t="n">
         <v>6.99</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>10.87</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42874</v>
+        <v>42877</v>
       </c>
       <c r="H12" t="n">
-        <v>18664.1</v>
+        <v>18263.35</v>
       </c>
       <c r="I12" t="n">
         <v>18265.83184583529</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="K12" t="n">
-        <v>20.91</v>
+        <v>18.32</v>
       </c>
       <c r="L12" t="n">
         <v>3.28</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>5</v>
+      </c>
+      <c r="U12" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>11.57</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42922</v>
+        <v>42923</v>
       </c>
       <c r="H13" t="n">
-        <v>18040.1</v>
+        <v>18365.8</v>
       </c>
       <c r="I13" t="n">
         <v>18051.05381738899</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K13" t="n">
-        <v>1.22</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="L13" t="n">
         <v>3.21</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>8.710000000000001</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42965</v>
+        <v>42968</v>
       </c>
       <c r="H14" t="n">
-        <v>17347.95</v>
+        <v>17128.8</v>
       </c>
       <c r="I14" t="n">
         <v>17244.39712682936</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K14" t="n">
-        <v>-5.54</v>
+        <v>-6.74</v>
       </c>
       <c r="L14" t="n">
         <v>8.74</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>10.75</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42985</v>
+        <v>42986</v>
       </c>
       <c r="H15" t="n">
-        <v>18556.75</v>
+        <v>18738.8</v>
       </c>
       <c r="I15" t="n">
         <v>18619.06509176559</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K15" t="n">
-        <v>-8.34</v>
+        <v>-9.4</v>
       </c>
       <c r="L15" t="n">
-        <v>9.5</v>
+        <v>9.76</v>
       </c>
       <c r="M15" t="n">
         <v>1.28</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>8.119999999999999</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43000</v>
+        <v>43003</v>
       </c>
       <c r="H16" t="n">
-        <v>17723.3</v>
+        <v>17555.95</v>
       </c>
       <c r="I16" t="n">
         <v>17717.53655227461</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K16" t="n">
-        <v>-5.42</v>
+        <v>-6.31</v>
       </c>
       <c r="L16" t="n">
-        <v>6.58</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="M16" t="n">
         <v>1.06</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>8.529999999999999</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43026</v>
+        <v>43031</v>
       </c>
       <c r="H17" t="n">
-        <v>18366.5</v>
+        <v>19247.2</v>
       </c>
       <c r="I17" t="n">
         <v>19053.76760426467</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="K17" t="n">
-        <v>-4.62</v>
+        <v>-9.630000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>7.97</v>
+        <v>11.67</v>
       </c>
       <c r="M17" t="n">
         <v>1.64</v>
       </c>
       <c r="N17" t="n">
-        <v>2.1</v>
+        <v>4.8</v>
       </c>
       <c r="O17" t="n">
         <v>-0.9399999999999999</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>10</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43056</v>
+        <v>43059</v>
       </c>
       <c r="H18" t="n">
-        <v>18279.2</v>
+        <v>17503.15</v>
       </c>
       <c r="I18" t="n">
         <v>17680.11648069035</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K18" t="n">
-        <v>-5.03</v>
+        <v>-9.06</v>
       </c>
       <c r="L18" t="n">
-        <v>7.83</v>
+        <v>10.06</v>
       </c>
       <c r="M18" t="n">
-        <v>2.39</v>
+        <v>2.89</v>
       </c>
       <c r="N18" t="n">
-        <v>2.1</v>
+        <v>4.25</v>
       </c>
       <c r="O18" t="n">
         <v>4.8</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>10</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43104</v>
+        <v>43105</v>
       </c>
       <c r="H19" t="n">
-        <v>17978.35</v>
+        <v>18964.5</v>
       </c>
       <c r="I19" t="n">
         <v>18203.59324484562</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.71</v>
+        <v>-8.35</v>
       </c>
       <c r="L19" t="n">
-        <v>5.01</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
       <c r="N19" t="n">
-        <v>3.05</v>
+        <v>5.49</v>
       </c>
       <c r="O19" t="n">
         <v>-4.25</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,25 +1799,25 @@
         <v>9.09</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43118</v>
+        <v>43119</v>
       </c>
       <c r="H20" t="n">
-        <v>18421.6</v>
+        <v>18354.6</v>
       </c>
       <c r="I20" t="n">
         <v>18364.24457633803</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.86</v>
+        <v>-3.22</v>
       </c>
       <c r="L20" t="n">
         <v>4.52</v>
       </c>
       <c r="M20" t="n">
-        <v>-0</v>
+        <v>0.33</v>
       </c>
       <c r="N20" t="n">
         <v>3.4</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>8.06</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43290</v>
+        <v>43291</v>
       </c>
       <c r="H21" t="n">
-        <v>16589.25</v>
+        <v>16804.8</v>
       </c>
       <c r="I21" t="n">
         <v>16668.82362053477</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K21" t="n">
-        <v>9.619999999999999</v>
+        <v>8.44</v>
       </c>
       <c r="L21" t="n">
         <v>1.34</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>116</v>
+        <v>117</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>7</v>
+      </c>
+      <c r="U21" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>9.02</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43350</v>
+        <v>43353</v>
       </c>
       <c r="H22" t="n">
-        <v>17954.45</v>
+        <v>17264.55</v>
       </c>
       <c r="I22" t="n">
         <v>17774.33213783008</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K22" t="n">
-        <v>6.84</v>
+        <v>2.74</v>
       </c>
       <c r="L22" t="n">
         <v>5.76</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>10.05</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43409</v>
+        <v>43410</v>
       </c>
       <c r="H23" t="n">
-        <v>14998.25</v>
+        <v>15363</v>
       </c>
       <c r="I23" t="n">
         <v>15178.75797757917</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K23" t="n">
-        <v>13.13</v>
+        <v>11.01</v>
       </c>
       <c r="L23" t="n">
         <v>3.88</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>14.25</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43475</v>
+        <v>43476</v>
       </c>
       <c r="H24" t="n">
-        <v>16496.15</v>
+        <v>15913.2</v>
       </c>
       <c r="I24" t="n">
         <v>15983.0973230326</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K24" t="n">
-        <v>7.38</v>
+        <v>3.58</v>
       </c>
       <c r="L24" t="n">
         <v>4.28</v>
@@ -1809,7 +2096,7 @@
         <v>1.99</v>
       </c>
       <c r="N24" t="n">
-        <v>2.44</v>
+        <v>3.53</v>
       </c>
       <c r="O24" t="n">
         <v>2.43</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>10.32</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43525</v>
+        <v>43529</v>
       </c>
       <c r="H25" t="n">
-        <v>16687.35</v>
+        <v>17246.3</v>
       </c>
       <c r="I25" t="n">
         <v>16767.91015264977</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K25" t="n">
-        <v>-4.86</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M25" t="n">
         <v>1.05</v>
       </c>
       <c r="N25" t="n">
-        <v>2.68</v>
+        <v>3.35</v>
       </c>
       <c r="O25" t="n">
         <v>-3.53</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>10.27</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43630</v>
+        <v>43633</v>
       </c>
       <c r="H26" t="n">
-        <v>20463.25</v>
+        <v>19991.75</v>
       </c>
       <c r="I26" t="n">
         <v>20087.56915973707</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="K26" t="n">
-        <v>18.65</v>
+        <v>15.92</v>
       </c>
       <c r="L26" t="n">
         <v>3.24</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>4</v>
+      </c>
+      <c r="U26" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>9.59</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43728</v>
+        <v>43731</v>
       </c>
       <c r="H27" t="n">
-        <v>19250.1</v>
+        <v>19918.3</v>
       </c>
       <c r="I27" t="n">
         <v>19469.1662350164</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="K27" t="n">
-        <v>3.71</v>
+        <v>0.37</v>
       </c>
       <c r="L27" t="n">
         <v>12.05</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>4</v>
+      </c>
+      <c r="U27" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>12.9</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43888</v>
+        <v>43889</v>
       </c>
       <c r="H28" t="n">
-        <v>23812.55</v>
+        <v>22670.95</v>
       </c>
       <c r="I28" t="n">
         <v>22946.65234287953</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K28" t="n">
-        <v>19.55</v>
+        <v>13.82</v>
       </c>
       <c r="L28" t="n">
         <v>11</v>
       </c>
       <c r="M28" t="n">
-        <v>1.26</v>
+        <v>1.73</v>
       </c>
       <c r="N28" t="n">
-        <v>2.57</v>
+        <v>4.79</v>
       </c>
       <c r="O28" t="n">
         <v>3.47</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>109</v>
+        <v>110</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>7</v>
+      </c>
+      <c r="U28" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>11.89</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43973</v>
+        <v>43977</v>
       </c>
       <c r="H29" t="n">
-        <v>19910.25</v>
+        <v>20667.3</v>
       </c>
       <c r="I29" t="n">
         <v>20559.89298205304</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="K29" t="n">
-        <v>12.18</v>
+        <v>8.84</v>
       </c>
       <c r="L29" t="n">
         <v>5.41</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>16.13</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>44071</v>
+        <v>44074</v>
       </c>
       <c r="H30" t="n">
-        <v>21329.55</v>
+        <v>20283</v>
       </c>
       <c r="I30" t="n">
         <v>21041.46518465544</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="K30" t="n">
-        <v>3.2</v>
+        <v>-1.86</v>
       </c>
       <c r="L30" t="n">
         <v>4.68</v>
@@ -2151,7 +2510,7 @@
         <v>2.59</v>
       </c>
       <c r="N30" t="n">
-        <v>4.11</v>
+        <v>4.91</v>
       </c>
       <c r="O30" t="n">
         <v>3.8</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43979</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>5</v>
+      </c>
+      <c r="U30" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>11.36</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>44104</v>
+        <v>44105</v>
       </c>
       <c r="H31" t="n">
-        <v>20256.95</v>
+        <v>20611</v>
       </c>
       <c r="I31" t="n">
         <v>20399.40253597941</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K31" t="n">
-        <v>0.13</v>
+        <v>-1.62</v>
       </c>
       <c r="L31" t="n">
         <v>6.25</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>9.890000000000001</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44216</v>
+        <v>44217</v>
       </c>
       <c r="H32" t="n">
-        <v>23979.95</v>
+        <v>23719</v>
       </c>
       <c r="I32" t="n">
         <v>23723.12189767656</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K32" t="n">
-        <v>16.35</v>
+        <v>15.08</v>
       </c>
       <c r="L32" t="n">
         <v>2.96</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>4</v>
+      </c>
+      <c r="U32" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>9.529999999999999</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44228</v>
+        <v>44229</v>
       </c>
       <c r="H33" t="n">
-        <v>24543.6</v>
+        <v>26432.55</v>
       </c>
       <c r="I33" t="n">
         <v>24925.2406612814</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K33" t="n">
-        <v>-3.48</v>
+        <v>-11.44</v>
       </c>
       <c r="L33" t="n">
-        <v>4.1</v>
+        <v>12.36</v>
       </c>
       <c r="M33" t="n">
         <v>1.5</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>14.82</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44306</v>
+        <v>44308</v>
       </c>
       <c r="H34" t="n">
-        <v>29320.7</v>
+        <v>28521.95</v>
       </c>
       <c r="I34" t="n">
         <v>28725.45250599465</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K34" t="n">
-        <v>10.93</v>
+        <v>7.9</v>
       </c>
       <c r="L34" t="n">
         <v>8.44</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>12.35</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44351</v>
+        <v>44354</v>
       </c>
       <c r="H35" t="n">
-        <v>28153.65</v>
+        <v>29155.8</v>
       </c>
       <c r="I35" t="n">
         <v>28894.5439968711</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K35" t="n">
-        <v>1.29</v>
+        <v>-2.22</v>
       </c>
       <c r="L35" t="n">
-        <v>2.38</v>
+        <v>2.89</v>
       </c>
       <c r="M35" t="n">
         <v>1.36</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>8.630000000000001</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44417</v>
+        <v>44418</v>
       </c>
       <c r="H36" t="n">
-        <v>28272.95</v>
+        <v>27117.65</v>
       </c>
       <c r="I36" t="n">
         <v>27576.18845743593</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K36" t="n">
-        <v>-3.03</v>
+        <v>-6.99</v>
       </c>
       <c r="L36" t="n">
         <v>7.94</v>
@@ -2493,7 +2924,7 @@
         <v>1.08</v>
       </c>
       <c r="N36" t="n">
-        <v>2.24</v>
+        <v>4.09</v>
       </c>
       <c r="O36" t="n">
         <v>3.56</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44371</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>10.05</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44438</v>
+        <v>44439</v>
       </c>
       <c r="H37" t="n">
-        <v>27157.85</v>
+        <v>28287.9</v>
       </c>
       <c r="I37" t="n">
         <v>28042.06095769318</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.15</v>
+        <v>-4.32</v>
       </c>
       <c r="L37" t="n">
-        <v>3.97</v>
+        <v>4.98</v>
       </c>
       <c r="M37" t="n">
         <v>0.85</v>
       </c>
       <c r="N37" t="n">
-        <v>1.29</v>
+        <v>4.16</v>
       </c>
       <c r="O37" t="n">
         <v>-4.09</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>9.17</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44468</v>
+        <v>44469</v>
       </c>
       <c r="H38" t="n">
-        <v>29382.4</v>
+        <v>28901.55</v>
       </c>
       <c r="I38" t="n">
         <v>28976.05452849566</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K38" t="n">
-        <v>3.87</v>
+        <v>2.17</v>
       </c>
       <c r="L38" t="n">
         <v>4.38</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>7.72</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44504</v>
+        <v>44508</v>
       </c>
       <c r="H39" t="n">
-        <v>29047.2</v>
+        <v>29526.55</v>
       </c>
       <c r="I39" t="n">
         <v>29231.82022641073</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.5</v>
+        <v>-2.16</v>
       </c>
       <c r="L39" t="n">
-        <v>2.42</v>
+        <v>3.17</v>
       </c>
       <c r="M39" t="n">
         <v>0.96</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,22 +3179,22 @@
         <v>7.43</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44517</v>
+        <v>44518</v>
       </c>
       <c r="H40" t="n">
-        <v>27691.05</v>
+        <v>27167.3</v>
       </c>
       <c r="I40" t="n">
         <v>27429.21271155045</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K40" t="n">
-        <v>-6.22</v>
+        <v>-7.99</v>
       </c>
       <c r="L40" t="n">
-        <v>6.46</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="M40" t="n">
         <v>0.54</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>9.42</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44575</v>
+        <v>44578</v>
       </c>
       <c r="H41" t="n">
-        <v>27078.45</v>
+        <v>27545.35</v>
       </c>
       <c r="I41" t="n">
         <v>27512.1292517309</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K41" t="n">
-        <v>0.33</v>
+        <v>-1.39</v>
       </c>
       <c r="L41" t="n">
         <v>3.16</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>8.26</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44581</v>
+        <v>44582</v>
       </c>
       <c r="H42" t="n">
-        <v>26072.35</v>
+        <v>25037.2</v>
       </c>
       <c r="I42" t="n">
         <v>25271.39559261044</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K42" t="n">
-        <v>-5.35</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="L42" t="n">
-        <v>5.77</v>
+        <v>9.92</v>
       </c>
       <c r="M42" t="n">
         <v>0.76</v>
       </c>
       <c r="N42" t="n">
-        <v>2.77</v>
+        <v>3.97</v>
       </c>
       <c r="O42" t="n">
         <v>1.72</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>10.35</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44652</v>
+        <v>44655</v>
       </c>
       <c r="H43" t="n">
-        <v>24612.85</v>
+        <v>24765.05</v>
       </c>
       <c r="I43" t="n">
         <v>24675.64053513737</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="K43" t="n">
-        <v>1.69</v>
+        <v>1.09</v>
       </c>
       <c r="L43" t="n">
         <v>3.39</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>4</v>
+      </c>
+      <c r="U43" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>8.23</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44686</v>
+        <v>44687</v>
       </c>
       <c r="H44" t="n">
-        <v>25088.65</v>
+        <v>23973.65</v>
       </c>
       <c r="I44" t="n">
         <v>24226.08722251838</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K44" t="n">
-        <v>1.31</v>
+        <v>-3.2</v>
       </c>
       <c r="L44" t="n">
-        <v>1.76</v>
+        <v>3.69</v>
       </c>
       <c r="M44" t="n">
         <v>0.98</v>
       </c>
       <c r="N44" t="n">
-        <v>3.95</v>
+        <v>4.44</v>
       </c>
       <c r="O44" t="n">
         <v>0.62</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>11.63</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44761</v>
+        <v>44762</v>
       </c>
       <c r="H45" t="n">
-        <v>20068.2</v>
+        <v>20208.2</v>
       </c>
       <c r="I45" t="n">
         <v>20163.76848871943</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K45" t="n">
-        <v>16.29</v>
+        <v>15.71</v>
       </c>
       <c r="L45" t="n">
         <v>4.53</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>6.59</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44824</v>
+        <v>44825</v>
       </c>
       <c r="H46" t="n">
-        <v>23242.7</v>
+        <v>22023.95</v>
       </c>
       <c r="I46" t="n">
         <v>22309.38389747696</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K46" t="n">
-        <v>15.02</v>
+        <v>8.99</v>
       </c>
       <c r="L46" t="n">
         <v>0.83</v>
@@ -3063,7 +3614,7 @@
         <v>3.09</v>
       </c>
       <c r="N46" t="n">
-        <v>2.89</v>
+        <v>5.24</v>
       </c>
       <c r="O46" t="n">
         <v>0.7</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>15.52</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44862</v>
+        <v>44865</v>
       </c>
       <c r="H47" t="n">
-        <v>21779.85</v>
+        <v>22740.5</v>
       </c>
       <c r="I47" t="n">
         <v>22589.7941624244</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K47" t="n">
-        <v>1.11</v>
+        <v>-3.25</v>
       </c>
       <c r="L47" t="n">
         <v>6.29</v>
@@ -3120,7 +3683,7 @@
         <v>1.5</v>
       </c>
       <c r="N47" t="n">
-        <v>2.68</v>
+        <v>4.41</v>
       </c>
       <c r="O47" t="n">
         <v>-5.24</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>10.71</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44949</v>
+        <v>44950</v>
       </c>
       <c r="H48" t="n">
-        <v>23037.05</v>
+        <v>22608.4</v>
       </c>
       <c r="I48" t="n">
         <v>23018.14089858081</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K48" t="n">
-        <v>1.3</v>
+        <v>-0.58</v>
       </c>
       <c r="L48" t="n">
         <v>4.31</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>9.81</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44958</v>
+        <v>44959</v>
       </c>
       <c r="H49" t="n">
-        <v>23916.95</v>
+        <v>24523.25</v>
       </c>
       <c r="I49" t="n">
         <v>23964.92475717155</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K49" t="n">
-        <v>-5.79</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="L49" t="n">
-        <v>9.119999999999999</v>
+        <v>9.25</v>
       </c>
       <c r="M49" t="n">
         <v>0.53</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>11.18</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45035</v>
+        <v>45036</v>
       </c>
       <c r="H50" t="n">
-        <v>24758.95</v>
+        <v>24254.4</v>
       </c>
       <c r="I50" t="n">
         <v>24555.92872261121</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K50" t="n">
-        <v>0.96</v>
+        <v>-1.1</v>
       </c>
       <c r="L50" t="n">
         <v>7.22</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>8.859999999999999</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45075</v>
+        <v>45076</v>
       </c>
       <c r="H51" t="n">
-        <v>25261.35</v>
+        <v>25586.95</v>
       </c>
       <c r="I51" t="n">
         <v>25515.08477613507</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K51" t="n">
-        <v>-4.15</v>
+        <v>-5.49</v>
       </c>
       <c r="L51" t="n">
-        <v>5.01</v>
+        <v>6.72</v>
       </c>
       <c r="M51" t="n">
         <v>0.67</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>8.119999999999999</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45100</v>
+        <v>45103</v>
       </c>
       <c r="H52" t="n">
-        <v>25145.25</v>
+        <v>23702.15</v>
       </c>
       <c r="I52" t="n">
         <v>24766.41190698381</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K52" t="n">
-        <v>-1.73</v>
+        <v>-7.37</v>
       </c>
       <c r="L52" t="n">
-        <v>3.44</v>
+        <v>11.65</v>
       </c>
       <c r="M52" t="n">
-        <v>0.34</v>
+        <v>10</v>
       </c>
       <c r="N52" t="n">
-        <v>1.99</v>
+        <v>5.74</v>
       </c>
       <c r="O52" t="n">
         <v>1.29</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>8.09</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45170</v>
+        <v>45173</v>
       </c>
       <c r="H53" t="n">
-        <v>24139.35</v>
+        <v>25671.55</v>
       </c>
       <c r="I53" t="n">
         <v>24722.63563971227</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K53" t="n">
-        <v>-1.84</v>
+        <v>-8.31</v>
       </c>
       <c r="L53" t="n">
-        <v>3.62</v>
+        <v>8.82</v>
       </c>
       <c r="M53" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="N53" t="n">
-        <v>2.5</v>
+        <v>6.35</v>
       </c>
       <c r="O53" t="n">
         <v>-5.74</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>4</v>
+      </c>
+      <c r="U53" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>7.81</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45230</v>
+        <v>45231</v>
       </c>
       <c r="H54" t="n">
-        <v>25655.05</v>
+        <v>25420.65</v>
       </c>
       <c r="I54" t="n">
         <v>25427.21731432718</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K54" t="n">
-        <v>-0.06</v>
+        <v>-0.98</v>
       </c>
       <c r="L54" t="n">
         <v>4.76</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>6.65</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="H55" t="n">
-        <v>26741.75</v>
+        <v>27026.55</v>
       </c>
       <c r="I55" t="n">
         <v>26995.77257848661</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K55" t="n">
-        <v>-5.2</v>
+        <v>-6.32</v>
       </c>
       <c r="L55" t="n">
-        <v>6.02</v>
+        <v>6.47</v>
       </c>
       <c r="M55" t="n">
         <v>0.67</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>5.73</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45295</v>
+        <v>45296</v>
       </c>
       <c r="H56" t="n">
-        <v>28357.9</v>
+        <v>27023.3</v>
       </c>
       <c r="I56" t="n">
         <v>27247.66795734694</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K56" t="n">
-        <v>4.93</v>
+        <v>-0.01</v>
       </c>
       <c r="L56" t="n">
         <v>1.49</v>
@@ -3633,7 +4304,7 @@
         <v>0.88</v>
       </c>
       <c r="N56" t="n">
-        <v>1.31</v>
+        <v>4.71</v>
       </c>
       <c r="O56" t="n">
         <v>1.07</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>8.67</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45316</v>
+        <v>45320</v>
       </c>
       <c r="H57" t="n">
-        <v>27948.8</v>
+        <v>28411.55</v>
       </c>
       <c r="I57" t="n">
         <v>28001.64401932431</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K57" t="n">
-        <v>-3.42</v>
+        <v>-5.14</v>
       </c>
       <c r="L57" t="n">
-        <v>4.54</v>
+        <v>6.76</v>
       </c>
       <c r="M57" t="n">
         <v>0.63</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>7.84</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45324</v>
+        <v>45327</v>
       </c>
       <c r="H58" t="n">
-        <v>28453.95</v>
+        <v>26954.8</v>
       </c>
       <c r="I58" t="n">
         <v>27354.5105866234</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K58" t="n">
-        <v>0.15</v>
+        <v>-5.13</v>
       </c>
       <c r="L58" t="n">
-        <v>1.72</v>
+        <v>6.03</v>
       </c>
       <c r="M58" t="n">
         <v>0.38</v>
       </c>
       <c r="N58" t="n">
-        <v>3.92</v>
+        <v>5.27</v>
       </c>
       <c r="O58" t="n">
         <v>1.66</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>15.07</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45414</v>
+        <v>45415</v>
       </c>
       <c r="H59" t="n">
-        <v>24827.2</v>
+        <v>25746.55</v>
       </c>
       <c r="I59" t="n">
         <v>25608.89419889939</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K59" t="n">
-        <v>7.89</v>
+        <v>4.48</v>
       </c>
       <c r="L59" t="n">
         <v>7.59</v>
@@ -3804,7 +4511,7 @@
         <v>1.92</v>
       </c>
       <c r="N59" t="n">
-        <v>3.02</v>
+        <v>3.7</v>
       </c>
       <c r="O59" t="n">
         <v>-5.27</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>4</v>
+      </c>
+      <c r="U59" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>8.41</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="H60" t="n">
-        <v>26834.8</v>
+        <v>26101.35</v>
       </c>
       <c r="I60" t="n">
         <v>26182.48259333196</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K60" t="n">
-        <v>4.23</v>
+        <v>1.38</v>
       </c>
       <c r="L60" t="n">
         <v>7.95</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>4</v>
+      </c>
+      <c r="U60" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>9.880000000000001</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45561</v>
+        <v>45562</v>
       </c>
       <c r="H61" t="n">
-        <v>26123.1</v>
+        <v>26247.9</v>
       </c>
       <c r="I61" t="n">
         <v>26143.31627040873</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K61" t="n">
-        <v>-0.08</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="L61" t="n">
         <v>3.8</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>3</v>
+      </c>
+      <c r="U61" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -3954,22 +4697,22 @@
         <v>5.96</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45574</v>
+        <v>45575</v>
       </c>
       <c r="H62" t="n">
-        <v>24975.05</v>
+        <v>24641.8</v>
       </c>
       <c r="I62" t="n">
         <v>24864.47943912465</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K62" t="n">
-        <v>-4.85</v>
+        <v>-6.12</v>
       </c>
       <c r="L62" t="n">
-        <v>5.3</v>
+        <v>6.28</v>
       </c>
       <c r="M62" t="n">
         <v>0.51</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>8.24</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45623</v>
+        <v>45624</v>
       </c>
       <c r="H63" t="n">
-        <v>25421.85</v>
+        <v>25545.6</v>
       </c>
       <c r="I63" t="n">
         <v>25544.90250906898</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K63" t="n">
-        <v>-3.17</v>
+        <v>-3.67</v>
       </c>
       <c r="L63" t="n">
         <v>4.55</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>7.34</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45650</v>
+        <v>45652</v>
       </c>
       <c r="H64" t="n">
-        <v>26707.7</v>
+        <v>26342.7</v>
       </c>
       <c r="I64" t="n">
         <v>26414.3530741282</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K64" t="n">
-        <v>4.55</v>
+        <v>3.12</v>
       </c>
       <c r="L64" t="n">
         <v>1.17</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,22 +4904,22 @@
         <v>7.73</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45686</v>
+        <v>45687</v>
       </c>
       <c r="H65" t="n">
-        <v>26651.35</v>
+        <v>26830.5</v>
       </c>
       <c r="I65" t="n">
         <v>26786.76359439837</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K65" t="n">
-        <v>-1.17</v>
+        <v>-1.85</v>
       </c>
       <c r="L65" t="n">
-        <v>2.78</v>
+        <v>3.91</v>
       </c>
       <c r="M65" t="n">
         <v>1.02</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>7.74</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45806</v>
+        <v>45807</v>
       </c>
       <c r="H66" t="n">
-        <v>29915</v>
+        <v>29595</v>
       </c>
       <c r="I66" t="n">
         <v>29648.98292785983</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K66" t="n">
-        <v>11.5</v>
+        <v>10.3</v>
       </c>
       <c r="L66" t="n">
         <v>1.53</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>5</v>
+      </c>
+      <c r="U66" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="67">
@@ -4239,22 +5042,22 @@
         <v>7.53</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45834</v>
+        <v>45835</v>
       </c>
       <c r="H67" t="n">
-        <v>30105</v>
+        <v>31030</v>
       </c>
       <c r="I67" t="n">
         <v>30140.32750661453</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K67" t="n">
-        <v>-1.72</v>
+        <v>-4.85</v>
       </c>
       <c r="L67" t="n">
-        <v>2.04</v>
+        <v>5.69</v>
       </c>
       <c r="M67" t="n">
         <v>0.64</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>7.69</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45873</v>
+        <v>45874</v>
       </c>
       <c r="H68" t="n">
-        <v>30645</v>
+        <v>30205</v>
       </c>
       <c r="I68" t="n">
         <v>30214.3014279682</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K68" t="n">
-        <v>-1.24</v>
+        <v>-2.66</v>
       </c>
       <c r="L68" t="n">
         <v>3.32</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>7.8</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46023</v>
+        <v>46024</v>
       </c>
       <c r="H69" t="n">
-        <v>26835</v>
+        <v>27045</v>
       </c>
       <c r="I69" t="n">
         <v>26935.15411950545</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K69" t="n">
-        <v>11.16</v>
+        <v>10.46</v>
       </c>
       <c r="L69" t="n">
         <v>5.68</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>102</v>
+        <v>103</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>6</v>
+      </c>
+      <c r="U69" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="70">
@@ -4410,28 +5249,28 @@
         <v>5.08</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46052</v>
+        <v>46054</v>
       </c>
       <c r="H70" t="n">
-        <v>26985</v>
+        <v>26385</v>
       </c>
       <c r="I70" t="n">
         <v>26483.71970011785</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K70" t="n">
-        <v>-0.22</v>
+        <v>-2.44</v>
       </c>
       <c r="L70" t="n">
-        <v>1.39</v>
+        <v>3.29</v>
       </c>
       <c r="M70" t="n">
         <v>0.83</v>
       </c>
       <c r="N70" t="n">
-        <v>1.72</v>
+        <v>2.22</v>
       </c>
       <c r="O70" t="n">
         <v>0.78</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -4467,19 +5318,19 @@
         <v>7.84</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="H71" t="n">
-        <v>24965</v>
+        <v>25110</v>
       </c>
       <c r="I71" t="n">
         <v>24982.94036687932</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K71" t="n">
-        <v>5.38</v>
+        <v>4.83</v>
       </c>
       <c r="L71" t="n">
         <v>4.4</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>3</v>
+      </c>
+      <c r="U71" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -4524,28 +5387,28 @@
         <v>8.859999999999999</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="H72" t="n">
-        <v>24085</v>
+        <v>23535</v>
       </c>
       <c r="I72" t="n">
         <v>23751.40017193836</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K72" t="n">
-        <v>-4.08</v>
+        <v>-6.27</v>
       </c>
       <c r="L72" t="n">
-        <v>5.22</v>
+        <v>6.77</v>
       </c>
       <c r="M72" t="n">
         <v>0.96</v>
       </c>
       <c r="N72" t="n">
-        <v>2.04</v>
+        <v>2.28</v>
       </c>
       <c r="O72" t="n">
         <v>0.58</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>3</v>
+      </c>
+      <c r="U72" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -4581,22 +5456,22 @@
         <v>7.86</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="H73" t="n">
-        <v>24970</v>
+        <v>25410</v>
       </c>
       <c r="I73" t="n">
         <v>25030.21985540806</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K73" t="n">
-        <v>-6.1</v>
+        <v>-7.97</v>
       </c>
       <c r="L73" t="n">
-        <v>8.16</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="M73" t="n">
         <v>2.07</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S73" t="b">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>1</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -4638,19 +5525,19 @@
         <v>8.140000000000001</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="H74" t="n">
-        <v>25570</v>
+        <v>25245</v>
       </c>
       <c r="I74" t="n">
         <v>25314.28206356979</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K74" t="n">
-        <v>0.63</v>
+        <v>-0.65</v>
       </c>
       <c r="L74" t="n">
         <v>2.54</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>3</v>
+      </c>
+      <c r="U74" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="75">
@@ -4695,19 +5594,19 @@
         <v>7.29</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="H75" t="n">
-        <v>22735</v>
+        <v>23540</v>
       </c>
       <c r="I75" t="n">
         <v>23192.83887851907</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="K75" t="n">
-        <v>9.94</v>
+        <v>6.75</v>
       </c>
       <c r="L75" t="n">
         <v>1.31</v>
@@ -4716,7 +5615,7 @@
         <v>1.75</v>
       </c>
       <c r="N75" t="n">
-        <v>2.91</v>
+        <v>3.54</v>
       </c>
       <c r="O75" t="n">
         <v>-1.27</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>3</v>
+      </c>
+      <c r="U75" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -4776,6 +5687,14 @@
       <c r="Q76" t="n">
         <v>3</v>
       </c>
+      <c r="R76" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="inlineStr"/>
+      <c r="U76" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9734,7 +10653,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>56.4</v>
+        <v>58.1</v>
       </c>
     </row>
     <row r="6">
@@ -9744,7 +10663,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>46.5</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="7">
@@ -9754,7 +10673,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="8">
@@ -9764,7 +10683,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -9774,7 +10693,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>74.8</v>
+        <v>75.8</v>
       </c>
     </row>
     <row r="10">
@@ -9784,7 +10703,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>99.5</v>
+        <v>102.2</v>
       </c>
     </row>
     <row r="11">
@@ -9794,7 +10713,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12">
@@ -9804,7 +10723,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13">
@@ -9814,7 +10733,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>32.4</v>
+        <v>29.7</v>
       </c>
     </row>
     <row r="14">
@@ -9824,7 +10743,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.32</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="15">
@@ -9834,7 +10753,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.95</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="16">
@@ -9844,7 +10763,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7</v>
+        <v>-2.01</v>
       </c>
     </row>
     <row r="17">
@@ -9854,7 +10773,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>51.15</v>
+        <v>47.99</v>
       </c>
     </row>
     <row r="18">
@@ -9864,7 +10783,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>51.4</v>
+        <v>35.1</v>
       </c>
     </row>
     <row r="19">
@@ -9874,7 +10793,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.47</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="20">
@@ -9884,7 +10803,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.88</v>
+        <v>6.14</v>
       </c>
     </row>
     <row r="21">
@@ -9894,7 +10813,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14.8</v>
+        <v>18.59</v>
       </c>
     </row>
     <row r="22">
@@ -9904,7 +10823,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23">
@@ -9914,7 +10833,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
@@ -9924,7 +10843,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="25">
@@ -9934,7 +10853,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5.2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26">
@@ -9944,7 +10863,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.65</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="27">
@@ -9964,7 +10883,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
     </row>
     <row r="29">
